--- a/config/中车_配置_v2.0.xlsx
+++ b/config/中车_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="3"/>
+    <workbookView windowWidth="15404" windowHeight="10825" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
   <si>
     <t>key</t>
   </si>
@@ -227,9 +227,6 @@
     <t>maxGap</t>
   </si>
   <si>
-    <t>pcs</t>
-  </si>
-  <si>
     <t>ModbusTCP</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
   </si>
   <si>
     <t>192.168.0.1</t>
-  </si>
-  <si>
-    <t>bms</t>
   </si>
   <si>
     <t>192.168.0.2</t>
@@ -2088,16 +2082,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F2" s="2">
         <v>1000</v>
@@ -2106,7 +2100,7 @@
         <v>1000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I2" s="2">
         <v>502</v>
@@ -2116,6 +2110,9 @@
       </c>
       <c r="R2" s="2">
         <v>50</v>
+      </c>
+      <c r="S2" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2124,16 +2121,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F3" s="2">
         <v>1000</v>
@@ -2142,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I3" s="2">
         <v>502</v>
@@ -2152,6 +2149,9 @@
       </c>
       <c r="R3" s="2">
         <v>50</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2178,16 +2178,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2198,7 +2198,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -2213,7 +2213,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -2228,7 +2228,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
@@ -2243,7 +2243,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -2258,7 +2258,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -2273,7 +2273,7 @@
         <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>

--- a/config/中车_配置_v2.0.xlsx
+++ b/config/中车_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15404" windowHeight="10825" activeTab="2"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="83">
   <si>
     <t>key</t>
   </si>
@@ -239,6 +240,12 @@
     <t>192.168.0.2</t>
   </si>
   <si>
+    <t>IEC104</t>
+  </si>
+  <si>
+    <t>./config/测控柜_中车.xlsx</t>
+  </si>
+  <si>
     <t>device_id</t>
   </si>
   <si>
@@ -267,6 +274,15 @@
   </si>
   <si>
     <t>/pds/pcs/1/yt</t>
+  </si>
+  <si>
+    <t>/pds/crd/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/crd/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/crd/0/yt</t>
   </si>
 </sst>
 </file>
@@ -916,7 +932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -924,6 +940,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1495,6 +1514,1430 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="遥测"/>
+      <sheetName val="遥信"/>
+      <sheetName val="遥控"/>
+      <sheetName val="遥脉"/>
+      <sheetName val="遥调"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>39</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>41</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>42</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>46</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>49</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>51</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>53</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>54</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>57</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>58</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>59</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>61</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>62</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>63</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>64</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>65</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>67</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>68</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>69</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>70</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>71</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>73</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>74</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>75</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>76</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>77</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>78</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>79</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>81</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>82</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>83</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>84</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>86</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>87</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>89</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>90</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>91</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>92</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>93</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>96</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>97</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>99</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>101</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>102</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>107</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>109</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>112</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>113</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>114</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>116</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>118</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>119</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>121</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>122</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>123</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>124</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>125</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>126</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>127</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>128</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>129</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>130</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>131</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>132</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>133</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>134</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>136</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>137</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>138</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>139</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>140</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>141</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>142</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>143</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>144</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>146</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>147</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>148</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>149</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>151</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>152</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>153</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>154</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>155</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>156</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>157</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>158</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>159</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>160</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>161</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>162</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>163</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>164</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>165</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>166</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>167</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>168</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>169</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="A2">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>1001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>1002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>1003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>1004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>1005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>1006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>1007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>1008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>1009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1015</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>1016</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>1017</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>1018</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>1019</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>1020</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>1021</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>1022</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>1023</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>1024</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>1025</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>1026</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>1027</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>1028</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>1029</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>1030</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>1031</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>1032</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>1033</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>1034</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>1035</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>1036</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>1037</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>1038</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>1039</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>1040</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>1041</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1042</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1043</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>1044</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>1045</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>1046</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>1047</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>1048</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>1049</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>1051</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>1052</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>1053</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>1054</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>1055</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>1056</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>1057</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>1058</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>1059</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>1060</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>1061</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>1062</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>1063</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>1064</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>1065</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>1066</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>1067</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>1068</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>1069</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>1070</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>1071</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>1072</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>1073</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>1074</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>1075</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>1076</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>1077</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>1078</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>1079</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>1080</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>1081</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>1082</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>1083</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>1084</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>1085</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>1086</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>1087</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>1088</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>1089</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>1090</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>1091</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>1092</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>1093</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>1094</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>1095</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>1096</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>1097</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>1098</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>1099</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>1100</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>1101</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>1102</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>1103</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>1104</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>1105</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>1106</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>1107</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="A2">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>3001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1999,8 +3442,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="2"/>
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.5952380952381" style="2" customWidth="1"/>
@@ -2048,22 +3491,22 @@
       <c r="J1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -2152,6 +3595,26 @@
       </c>
       <c r="S3" s="2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2404</v>
       </c>
     </row>
   </sheetData>
@@ -2164,13 +3627,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.0952380952381" style="2" customWidth="1"/>
-    <col min="3" max="3" width="212.15873015873" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.3968253968254" style="2" customWidth="1"/>
+    <col min="3" max="3" width="184.373015873016" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.17460317460317" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.2936507936508" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.4365079365079" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.11111111111111" style="2"/>
@@ -2178,16 +3641,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2198,7 +3661,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -2213,7 +3676,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -2228,7 +3691,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
@@ -2243,7 +3706,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -2258,7 +3721,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -2273,13 +3736,58 @@
         <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
         <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2021,2020,2022,2023,2024,2025,2026,2027,2028,2029</v>
       </c>
       <c r="D7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$170)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$170)</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$170)</f>
+        <v>3000,3001,3002</v>
+      </c>
+      <c r="D10" s="4">
         <v>1</v>
       </c>
     </row>
